--- a/Assets/ExcelDatas/PhaseData.xlsx
+++ b/Assets/ExcelDatas/PhaseData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YH\Git\Project_Advence\Assets\ExcelDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectGit\Project_Advence_g\Assets\ExcelDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C4C776D-EC99-4F81-B656-A1E3DF3CB461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DBCF8F-3190-4829-AFC9-475B45CD245C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3165" windowWidth="20595" windowHeight="13260" firstSheet="1" activeTab="1" xr2:uid="{00B68857-C6E1-4D98-82FE-3C4F502D76E8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00B68857-C6E1-4D98-82FE-3C4F502D76E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Define" sheetId="7" state="hidden" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>ALL:KEY</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,14 +219,6 @@
   </si>
   <si>
     <t>PhaseNumber</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PatternMin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PatternMax</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -312,47 +304,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="0"/>
@@ -583,19 +535,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}" name="표2" displayName="표2" ref="A3:L9" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
-  <autoFilter ref="A3:L9" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{513471B3-6400-4B91-8068-618BE05D815D}" name="Index" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{CD7519DA-C7A5-4013-9D1E-02930E6F874D}" name="Name" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{CC8E0CCD-C85C-46BA-929C-F5BBFB5A1A79}" name="Stage" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{CFA3003B-F438-4CE9-99FA-0BDE8A71B7CF}" name="PhaseNumber" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{8625A633-6A8D-417D-BBE6-80F0F4A00567}" name="Background_Local" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{BF845FF7-45A1-459C-90FB-8D626C86D914}" name="ScrollSpeed" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{10204976-6592-4FB9-951E-15CCC0EC3849}" name="FirstPrintMonster" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{9A6465BD-2936-47C4-855B-716B5E435C3F}" name="TargetMonsterValue" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{FA1A94B9-BAC2-4255-81C5-CD7CB07A2541}" name="PatternMin" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{D3C830BE-4E63-4B2C-99D7-89C507CB395A}" name="PatternMax" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}" name="표2" displayName="표2" ref="A3:J9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A3:J9" xr:uid="{069061F9-1BA1-478D-A8D7-D7B6EB1F4CA2}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{513471B3-6400-4B91-8068-618BE05D815D}" name="Index" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{CD7519DA-C7A5-4013-9D1E-02930E6F874D}" name="Name" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{CC8E0CCD-C85C-46BA-929C-F5BBFB5A1A79}" name="Stage" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{CFA3003B-F438-4CE9-99FA-0BDE8A71B7CF}" name="PhaseNumber" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{8625A633-6A8D-417D-BBE6-80F0F4A00567}" name="Background_Local" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{BF845FF7-45A1-459C-90FB-8D626C86D914}" name="ScrollSpeed" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{10204976-6592-4FB9-951E-15CCC0EC3849}" name="FirstPrintMonster" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{9A6465BD-2936-47C4-855B-716B5E435C3F}" name="TargetMonsterValue" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{90AFA540-4A82-42E5-8C46-9C6D41BDA798}" name="PhaseValue1" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{A49A88B8-CCBE-4536-8B75-2413F30D3B51}" name="PhaseValue2" dataDxfId="0"/>
   </tableColumns>
@@ -604,9 +554,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -644,7 +594,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -750,7 +700,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -892,7 +842,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1082,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A9E828-B25D-49C6-B4AF-221979A45248}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" style="2" bestFit="1" customWidth="1"/>
@@ -1092,13 +1042,11 @@
     <col min="6" max="6" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.75" style="3"/>
+    <col min="9" max="10" width="14.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.75" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
@@ -1124,19 +1072,13 @@
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1162,19 +1104,13 @@
         <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1200,19 +1136,13 @@
         <v>35</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>50</v>
       </c>
@@ -1238,19 +1168,13 @@
         <v>600</v>
       </c>
       <c r="I4" s="2">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="J4" s="2">
-        <v>2028</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="L4" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>51</v>
       </c>
@@ -1276,19 +1200,13 @@
         <v>650</v>
       </c>
       <c r="I5" s="2">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="J5" s="2">
-        <v>2028</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>52</v>
       </c>
@@ -1314,19 +1232,13 @@
         <v>700</v>
       </c>
       <c r="I6" s="2">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="J6" s="2">
-        <v>2028</v>
-      </c>
-      <c r="K6" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="L6" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>53</v>
       </c>
@@ -1352,19 +1264,13 @@
         <v>750</v>
       </c>
       <c r="I7" s="2">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="J7" s="2">
-        <v>2028</v>
-      </c>
-      <c r="K7" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="L7" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>54</v>
       </c>
@@ -1390,19 +1296,13 @@
         <v>800</v>
       </c>
       <c r="I8" s="2">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="J8" s="2">
-        <v>2028</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="L8" s="2">
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>55</v>
       </c>
@@ -1428,15 +1328,9 @@
         <v>850</v>
       </c>
       <c r="I9" s="2">
-        <v>2000</v>
+        <v>0.8</v>
       </c>
       <c r="J9" s="2">
-        <v>2028</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="L9" s="2">
         <v>1.2</v>
       </c>
     </row>
